--- a/Outputs/repeated_holdout_cross_val_50_Fertility.xlsx
+++ b/Outputs/repeated_holdout_cross_val_50_Fertility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Generalized_Decision_Trees\Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3FA229-78E1-4C6D-9FAB-2F71DFB86156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E40724-6818-4F1D-B63E-2839360C4257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,27 +24,20 @@
     <sheet name="Summary" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Kaniadakis!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Kapur!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Renyi!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Shannon!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sharma_Mittal!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sharma_Taneja!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tsallis!$A$1:$G$1</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">Summary!$A$1</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Summary!$A$2:$A$51</definedName>
     <definedName name="_xlchart.v1.10" hidden="1">Summary!$F$1</definedName>
     <definedName name="_xlchart.v1.11" hidden="1">Summary!$F$2:$F$51</definedName>
     <definedName name="_xlchart.v1.12" hidden="1">Summary!$G$1</definedName>
     <definedName name="_xlchart.v1.13" hidden="1">Summary!$G$2:$G$51</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Summary!$A$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Summary!$A$2:$A$51</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Summary!$B$1</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Summary!$B$2:$B$51</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Summary!$C$1</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Summary!$C$2:$C$51</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Summary!$B$1</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Summary!$D$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Summary!$D$2:$D$51</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Summary!$E$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Summary!$E$2:$E$51</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Summary!$F$1</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Summary!$F$2:$F$51</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Summary!$G$1</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Summary!$G$2:$G$51</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">Summary!$B$2:$B$51</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">Summary!$C$1</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">Summary!$C$2:$C$51</definedName>
@@ -165,37 +158,37 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.15</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.17</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.19</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.21</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.25</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="6">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.27</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -244,7 +237,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{838BB3B6-071A-4C54-BF50-DFE92BBAF832}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Shannon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -257,7 +250,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{994DEFF3-D8E6-4589-97C0-50D2B1A062D0}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.16</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Renyi</cx:v>
             </cx:txData>
           </cx:tx>
@@ -270,7 +263,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{927E8329-FD0D-4A98-9BF4-A5662402C706}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.18</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Sharma-Mittal</cx:v>
             </cx:txData>
           </cx:tx>
@@ -283,7 +276,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{652374FF-6BF0-4200-9B84-D7265774D02E}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.20</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Tsallis</cx:v>
             </cx:txData>
           </cx:tx>
@@ -296,7 +289,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6B681C34-7A4C-4B27-BF43-5A997CCA2320}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.22</cx:f>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>Sharma-Taneja</cx:v>
             </cx:txData>
           </cx:tx>
@@ -309,7 +302,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{B5B7AC4F-9FAB-4F94-8B8D-F8F32CA2CB4C}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.24</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Kapur</cx:v>
             </cx:txData>
           </cx:tx>
@@ -322,7 +315,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{DF39A4BA-83FC-4050-BA02-0DD3C51B9116}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.26</cx:f>
+              <cx:f>_xlchart.v1.12</cx:f>
               <cx:v>Kaniadakis</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1290,33 +1283,33 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.83870967741935498</v>
+        <v>0.54838709677419395</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
-      </c>
-      <c r="E2">
-        <v>0.44444444444444398</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F2">
-        <v>281</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.74193548387096797</v>
+        <v>0.58064516129032295</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1325,58 +1318,58 @@
         <v>#NUM!</v>
       </c>
       <c r="F3">
-        <v>202</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.77419354838709697</v>
+        <v>0.61290322580645196</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E4">
-        <v>0.36363636363636398</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="F4">
-        <v>853</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.77419354838709697</v>
+        <v>0.64516129032258096</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>0.25</v>
-      </c>
-      <c r="E5">
-        <v>0.22222222222222199</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F5">
-        <v>373</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.83870967741935498</v>
+        <v>0.64516129032258096</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1385,39 +1378,39 @@
         <v>#NUM!</v>
       </c>
       <c r="F6">
-        <v>89</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.87096774193548399</v>
+        <v>0.64516129032258096</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>0.25</v>
       </c>
       <c r="E7">
-        <v>0.33333333333333298</v>
+        <v>0.15384615384615399</v>
       </c>
       <c r="F7">
-        <v>546</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.64516129032258096</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
       <c r="D8">
         <v>0</v>
       </c>
@@ -1425,47 +1418,47 @@
         <v>#NUM!</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.64516129032258096</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E9">
+        <v>0.16666666666666699</v>
       </c>
       <c r="F9">
-        <v>662</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.87096774193548399</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
-      </c>
-      <c r="E10">
-        <v>0.33333333333333298</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F10">
-        <v>45</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1473,70 +1466,70 @@
         <v>0.67741935483870996</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E11">
+        <v>0.16666666666666699</v>
       </c>
       <c r="F11">
-        <v>763</v>
+        <v>661</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.67741935483870996</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>0.25</v>
       </c>
       <c r="E12">
-        <v>0.16666666666666699</v>
+        <v>0.18181818181818199</v>
       </c>
       <c r="F12">
-        <v>589</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.87096774193548399</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>0.18181818181818199</v>
       </c>
       <c r="F13">
-        <v>292</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>0.80645161290322598</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1545,18 +1538,18 @@
         <v>#NUM!</v>
       </c>
       <c r="F14">
-        <v>903</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.77419354838709697</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1565,261 +1558,267 @@
         <v>#NUM!</v>
       </c>
       <c r="F15">
-        <v>848</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0.80645161290322598</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E16">
+        <v>0.2</v>
       </c>
       <c r="F16">
-        <v>461</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>0.80645161290322598</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D17">
-        <v>0.5</v>
-      </c>
-      <c r="E17">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F17">
-        <v>926</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.77419354838709697</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>0.25</v>
       </c>
       <c r="E18">
-        <v>0.22222222222222199</v>
+        <v>0.2</v>
       </c>
       <c r="F18">
-        <v>407</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.87096774193548399</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E19">
+        <v>0.36363636363636398</v>
       </c>
       <c r="F19">
-        <v>576</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0.74193548387096797</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E20">
+        <v>0.22222222222222199</v>
       </c>
       <c r="F20">
-        <v>508</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>0.83870967741935498</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21">
         <v>7</v>
       </c>
-      <c r="C21">
-        <v>8</v>
-      </c>
       <c r="D21">
-        <v>0.5</v>
-      </c>
-      <c r="E21">
-        <v>0.44444444444444398</v>
+        <v>0</v>
+      </c>
+      <c r="E21" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F21">
-        <v>612</v>
+        <v>848</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.87096774193548399</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>0.22222222222222199</v>
       </c>
       <c r="F22">
-        <v>560</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>0.70967741935483897</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>0.25</v>
-      </c>
-      <c r="E23">
-        <v>0.18181818181818199</v>
+        <v>0</v>
+      </c>
+      <c r="E23" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F23">
-        <v>211</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0.80645161290322598</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <v>0.25</v>
       </c>
       <c r="E24">
-        <v>0.25</v>
+        <v>0.22222222222222199</v>
       </c>
       <c r="F24">
-        <v>755</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.80645161290322598</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>0.25</v>
       </c>
       <c r="E25">
-        <v>0.25</v>
+        <v>0.22222222222222199</v>
       </c>
       <c r="F25">
-        <v>353</v>
+        <v>789</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>0.67741935483870996</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B26">
         <v>8</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E26">
+        <v>0.22222222222222199</v>
       </c>
       <c r="F26">
-        <v>737</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.80645161290322598</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D27">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
-        <v>0.25</v>
+        <v>0.36363636363636398</v>
       </c>
       <c r="F27">
-        <v>423</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.87096774193548399</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>0.25</v>
-      </c>
-      <c r="E28">
-        <v>0.33333333333333298</v>
+        <v>0</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F28">
-        <v>697</v>
+        <v>903</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1827,10 +1826,10 @@
         <v>0.80645161290322598</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1839,47 +1838,47 @@
         <v>#NUM!</v>
       </c>
       <c r="F29">
-        <v>431</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>0.67741935483870996</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E30">
-        <v>0.16666666666666699</v>
+        <v>0.4</v>
       </c>
       <c r="F30">
-        <v>661</v>
+        <v>926</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>0.61290322580645196</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>0.25</v>
       </c>
       <c r="E31">
-        <v>0.14285714285714299</v>
+        <v>0.25</v>
       </c>
       <c r="F31">
-        <v>424</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1887,10 +1886,10 @@
         <v>0.80645161290322598</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D32">
         <v>0.25</v>
@@ -1899,12 +1898,12 @@
         <v>0.25</v>
       </c>
       <c r="F32">
-        <v>123</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>0.74193548387096797</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -1916,18 +1915,18 @@
         <v>0.25</v>
       </c>
       <c r="E33">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F33">
-        <v>345</v>
+        <v>423</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -1939,38 +1938,38 @@
         <v>#NUM!</v>
       </c>
       <c r="F34">
-        <v>374</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D35">
         <v>0.25</v>
       </c>
       <c r="E35">
-        <v>0.22222222222222199</v>
+        <v>0.25</v>
       </c>
       <c r="F35">
-        <v>660</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0.74193548387096797</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B36">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1979,58 +1978,58 @@
         <v>#NUM!</v>
       </c>
       <c r="F36">
-        <v>543</v>
+        <v>701</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0.54838709677419395</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E37">
+        <v>0.25</v>
       </c>
       <c r="F37">
-        <v>242</v>
+        <v>681</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>0.90322580645161299</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B38">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D38">
         <v>0.5</v>
       </c>
       <c r="E38">
-        <v>0.57142857142857195</v>
+        <v>0.44444444444444398</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0.58064516129032295</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2039,55 +2038,55 @@
         <v>#NUM!</v>
       </c>
       <c r="F39">
-        <v>711</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.64516129032258096</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E40">
-        <v>0.15384615384615399</v>
+        <v>0.44444444444444398</v>
       </c>
       <c r="F40">
-        <v>92</v>
+        <v>612</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.80645161290322598</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>8</v>
       </c>
       <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="E41">
+        <v>0.28571428571428598</v>
       </c>
       <c r="F41">
-        <v>701</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.74193548387096797</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -2096,90 +2095,90 @@
         <v>0.25</v>
       </c>
       <c r="E42">
-        <v>0.2</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="F42">
-        <v>168</v>
+        <v>842</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0.77419354838709697</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>0.25</v>
       </c>
       <c r="E43">
-        <v>0.22222222222222199</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="F43">
-        <v>789</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0.83870967741935498</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
         <v>7</v>
       </c>
-      <c r="C44">
-        <v>8</v>
-      </c>
       <c r="D44">
         <v>0.25</v>
       </c>
       <c r="E44">
-        <v>0.28571428571428598</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="F44">
-        <v>514</v>
+        <v>546</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.70967741935483897</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>0.25</v>
       </c>
       <c r="E45">
-        <v>0.18181818181818199</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="F45">
-        <v>852</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0.83870967741935498</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E46">
-        <v>0.28571428571428598</v>
+        <v>0.5</v>
       </c>
       <c r="F46">
-        <v>842</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2187,102 +2186,101 @@
         <v>0.87096774193548399</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>0.25</v>
-      </c>
-      <c r="E47">
-        <v>0.33333333333333298</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>994</v>
+        <v>576</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.77419354838709697</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>0.25</v>
-      </c>
-      <c r="E48">
-        <v>0.22222222222222199</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>583</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.80645161290322598</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B49">
         <v>9</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49">
         <v>0.25</v>
       </c>
       <c r="E49">
-        <v>0.25</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="F49">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>0.83870967741935498</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D50">
         <v>0.25</v>
       </c>
       <c r="E50">
-        <v>0.28571428571428598</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="F50">
-        <v>164</v>
+        <v>994</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>0.77419354838709697</v>
+        <v>0.90322580645161299</v>
       </c>
       <c r="B51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D51">
         <v>0.5</v>
       </c>
       <c r="E51">
-        <v>0.36363636363636398</v>
+        <v>0.57142857142857195</v>
       </c>
       <c r="F51">
-        <v>386</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F51">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2318,39 +2316,39 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.80645161290322598</v>
+        <v>0.54838709677419395</v>
       </c>
       <c r="B2">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
-      </c>
-      <c r="F2">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="F2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G2">
-        <v>281</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.70967741935483897</v>
+        <v>0.64516129032258096</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2359,21 +2357,21 @@
         <v>#NUM!</v>
       </c>
       <c r="G3">
-        <v>202</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.80645161290322598</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2382,110 +2380,113 @@
         <v>#NUM!</v>
       </c>
       <c r="G4">
-        <v>853</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.74193548387096797</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B5">
         <v>0.5</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F5">
+        <v>0.16666666666666699</v>
       </c>
       <c r="G5">
-        <v>373</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.83870967741935498</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B6">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F6">
+        <v>0.16666666666666699</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.87096774193548399</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F7">
-        <v>0.5</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="G7">
-        <v>546</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.87096774193548399</v>
+        <v>0.67741935483870996</v>
       </c>
       <c r="B8">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="F8">
+        <v>0.16666666666666699</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.64516129032258096</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B9">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2494,18 +2495,18 @@
         <v>#NUM!</v>
       </c>
       <c r="G9">
-        <v>662</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.74193548387096797</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B10">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>13</v>
@@ -2517,90 +2518,90 @@
         <v>#NUM!</v>
       </c>
       <c r="G10">
-        <v>45</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>0.67741935483870996</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F11">
+        <v>0.18181818181818199</v>
       </c>
       <c r="G11">
-        <v>763</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.67741935483870996</v>
+        <v>0.70967741935483897</v>
       </c>
       <c r="B12">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>0.25</v>
-      </c>
-      <c r="F12">
-        <v>0.16666666666666699</v>
+        <v>0</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G12">
-        <v>589</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.77419354838709697</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>0.25</v>
-      </c>
-      <c r="F13">
-        <v>0.22222222222222199</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G13">
-        <v>292</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>0.80645161290322598</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B14">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2609,67 +2610,67 @@
         <v>#NUM!</v>
       </c>
       <c r="G14">
-        <v>903</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.70967741935483897</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B15">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="e">
-        <v>#NUM!</v>
+        <v>0.5</v>
+      </c>
+      <c r="F15">
+        <v>0.33333333333333298</v>
       </c>
       <c r="G15">
-        <v>848</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0.77419354838709697</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B16">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="e">
-        <v>#NUM!</v>
+        <v>0.5</v>
+      </c>
+      <c r="F16">
+        <v>0.33333333333333298</v>
       </c>
       <c r="G16">
-        <v>461</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>0.83870967741935498</v>
+        <v>0.74193548387096797</v>
       </c>
       <c r="B17">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2678,64 +2679,67 @@
         <v>#NUM!</v>
       </c>
       <c r="G17">
-        <v>926</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.80645161290322598</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
         <v>4</v>
       </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
       <c r="D18">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>0.25</v>
       </c>
       <c r="F18">
-        <v>0.25</v>
+        <v>0.22222222222222199</v>
       </c>
       <c r="G18">
-        <v>407</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.87096774193548399</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B19">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
+      <c r="F19" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="G19">
-        <v>576</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0.83870967741935498</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2744,12 +2748,12 @@
         <v>#NUM!</v>
       </c>
       <c r="G20">
-        <v>508</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>0.67741935483870996</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -2758,59 +2762,62 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>0.25</v>
-      </c>
-      <c r="F21">
-        <v>0.16666666666666699</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G21">
-        <v>612</v>
+        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.87096774193548399</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="F22">
+        <v>0.22222222222222199</v>
       </c>
       <c r="G22">
-        <v>560</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>0.70967741935483897</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B23">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>0.25</v>
       </c>
       <c r="F23">
-        <v>0.18181818181818199</v>
+        <v>0.22222222222222199</v>
       </c>
       <c r="G23">
-        <v>211</v>
+        <v>661</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2818,45 +2825,45 @@
         <v>0.77419354838709697</v>
       </c>
       <c r="B24">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="e">
-        <v>#NUM!</v>
+        <v>0.5</v>
+      </c>
+      <c r="F24">
+        <v>0.36363636363636398</v>
       </c>
       <c r="G24">
-        <v>755</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.80645161290322598</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B25">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="F25" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G25">
-        <v>353</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2864,13 +2871,13 @@
         <v>0.77419354838709697</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2879,145 +2886,145 @@
         <v>#NUM!</v>
       </c>
       <c r="G26">
-        <v>737</v>
+        <v>660</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.74193548387096797</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B27">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
-      </c>
-      <c r="F27">
-        <v>0.33333333333333298</v>
+        <v>0</v>
+      </c>
+      <c r="F27" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G27">
-        <v>423</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.87096774193548399</v>
+        <v>0.77419354838709697</v>
       </c>
       <c r="B28">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>0.25</v>
       </c>
       <c r="F28">
-        <v>0.33333333333333298</v>
+        <v>0.22222222222222199</v>
       </c>
       <c r="G28">
-        <v>697</v>
+        <v>852</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B29">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29">
         <v>12</v>
       </c>
-      <c r="D29">
-        <v>14</v>
-      </c>
       <c r="E29">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
-        <v>0.22222222222222199</v>
+        <v>0.4</v>
       </c>
       <c r="G29">
-        <v>431</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B30">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>0.25</v>
-      </c>
-      <c r="F30">
-        <v>0.22222222222222199</v>
+        <v>0</v>
+      </c>
+      <c r="F30" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G30">
-        <v>661</v>
+        <v>853</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B31">
         <v>0.5</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
-      </c>
-      <c r="F31">
-        <v>0.36363636363636398</v>
+        <v>0</v>
+      </c>
+      <c r="F31" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G31">
-        <v>424</v>
+        <v>903</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F32">
+        <v>0.25</v>
       </c>
       <c r="G32">
-        <v>123</v>
+        <v>407</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -3025,105 +3032,105 @@
         <v>0.80645161290322598</v>
       </c>
       <c r="B33">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E33">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G33">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>0.74193548387096797</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
         <v>8</v>
       </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F34">
-        <v>0.33333333333333298</v>
+        <v>0.25</v>
       </c>
       <c r="G34">
-        <v>374</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0.77419354838709697</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B35">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F35">
+        <v>0.25</v>
       </c>
       <c r="G35">
-        <v>660</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0.70967741935483897</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B36">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="e">
-        <v>#NUM!</v>
+        <v>0.5</v>
+      </c>
+      <c r="F36">
+        <v>0.4</v>
       </c>
       <c r="G36">
-        <v>543</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0.54838709677419395</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B37">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3132,84 +3139,87 @@
         <v>#NUM!</v>
       </c>
       <c r="G37">
-        <v>242</v>
+        <v>994</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>0.87096774193548399</v>
+        <v>0.80645161290322598</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
+      <c r="F38" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="G38">
-        <v>5</v>
+        <v>583</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0.67741935483870996</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B39">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>0.25</v>
-      </c>
-      <c r="F39">
-        <v>0.16666666666666699</v>
+        <v>0</v>
+      </c>
+      <c r="F39" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G39">
-        <v>711</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.80645161290322598</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B40">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>0.25</v>
-      </c>
-      <c r="F40">
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+      <c r="F40" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="G40">
-        <v>92</v>
+        <v>926</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.74193548387096797</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B41">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>9</v>
@@ -3221,53 +3231,53 @@
         <v>#NUM!</v>
       </c>
       <c r="G41">
-        <v>701</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.80645161290322598</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B42">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42">
         <v>8</v>
       </c>
-      <c r="D42">
-        <v>9</v>
-      </c>
       <c r="E42">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F42">
-        <v>0.4</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="G42">
-        <v>168</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0.77419354838709697</v>
+        <v>0.83870967741935498</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="e">
-        <v>#NUM!</v>
+        <v>0.25</v>
+      </c>
+      <c r="F43">
+        <v>0.28571428571428598</v>
       </c>
       <c r="G43">
-        <v>789</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -3275,186 +3285,179 @@
         <v>0.83870967741935498</v>
       </c>
       <c r="B44">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F44">
-        <v>0.28571428571428598</v>
+        <v>0.54545454545454497</v>
       </c>
       <c r="G44">
-        <v>514</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.77419354838709697</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B45">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F45">
-        <v>0.22222222222222199</v>
+        <v>0.5</v>
       </c>
       <c r="G45">
-        <v>852</v>
+        <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0.93548387096774199</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B46">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E46">
-        <v>0.5</v>
-      </c>
-      <c r="F46">
-        <v>0.66666666666666696</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>842</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>0.80645161290322598</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="D47">
         <v>7</v>
       </c>
-      <c r="D47">
-        <v>11</v>
-      </c>
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47" t="e">
-        <v>#NUM!</v>
-      </c>
       <c r="G47">
-        <v>994</v>
+        <v>576</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.80645161290322598</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48" t="e">
-        <v>#NUM!</v>
-      </c>
       <c r="G48">
-        <v>583</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.67741935483870996</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B49">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49">
         <v>0.25</v>
       </c>
       <c r="F49">
-        <v>0.16666666666666699</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="G49">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>0.83870967741935498</v>
+        <v>0.87096774193548399</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="G50">
         <v>5</v>
-      </c>
-      <c r="D50">
-        <v>7</v>
-      </c>
-      <c r="E50">
-        <v>0.25</v>
-      </c>
-      <c r="F50">
-        <v>0.28571428571428598</v>
-      </c>
-      <c r="G50">
-        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>0.83870967741935498</v>
+        <v>0.93548387096774199</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E51">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F51">
-        <v>0.54545454545454497</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="G51">
-        <v>386</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4777,6 +4780,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5958,6 +5962,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -7292,6 +7297,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -8614,6 +8620,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9792,6 +9799,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
